--- a/TestData/LV_TMTT0048829_VerifyStaffRoleChangesImplementedOnInternalTeamForCaptialSolution.xlsx
+++ b/TestData/LV_TMTT0048829_VerifyStaffRoleChangesImplementedOnInternalTeamForCaptialSolution.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4035D091-827F-4ABC-8944-C2C7241D822D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA25EFDB-50E1-4423-B13A-9E74A7C7F3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="2" r:id="rId1"/>
-    <sheet name="AppName" sheetId="3" r:id="rId2"/>
-    <sheet name="ModuleName" sheetId="4" r:id="rId3"/>
+    <sheet name="AppName" sheetId="3" r:id="rId1"/>
+    <sheet name="ModuleName" sheetId="4" r:id="rId2"/>
+    <sheet name="UsersFinancial" sheetId="2" r:id="rId3"/>
+    <sheet name="UsersNonFinancial" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="72">
   <si>
     <t>StdUser</t>
   </si>
@@ -41,9 +42,6 @@
     <t>Project Neon</t>
   </si>
   <si>
-    <t>Project Alpha</t>
-  </si>
-  <si>
     <t>App Name</t>
   </si>
   <si>
@@ -71,9 +69,6 @@
     <t>Number</t>
   </si>
   <si>
-    <t>LOB</t>
-  </si>
-  <si>
     <t>Primary Capital Advisory</t>
   </si>
   <si>
@@ -161,9 +156,6 @@
     <t xml:space="preserve">Registered </t>
   </si>
   <si>
-    <t>Buyside &amp; Financing Advisory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Not Capital Solution </t>
   </si>
   <si>
@@ -173,9 +165,6 @@
     <t>RecordType</t>
   </si>
   <si>
-    <t>63479</t>
-  </si>
-  <si>
     <t>Philip Keffer</t>
   </si>
   <si>
@@ -221,13 +210,40 @@
     <t>TMTI0123340</t>
   </si>
   <si>
-    <t xml:space="preserve">Mark Fishr </t>
-  </si>
-  <si>
     <t>Non US Non Capital Solution</t>
   </si>
   <si>
     <t>TMTI0123342</t>
+  </si>
+  <si>
+    <t>JobType</t>
+  </si>
+  <si>
+    <t>Alec Ellison</t>
+  </si>
+  <si>
+    <t>TMTI0123344</t>
+  </si>
+  <si>
+    <t>Mark Fisher</t>
+  </si>
+  <si>
+    <t>TMTI0123349</t>
+  </si>
+  <si>
+    <t>Ryan Carey</t>
+  </si>
+  <si>
+    <t>TMTI0123351</t>
+  </si>
+  <si>
+    <t>Emre Abale </t>
+  </si>
+  <si>
+    <t>TMTI0123353</t>
+  </si>
+  <si>
+    <t>TMTI0123299</t>
   </si>
 </sst>
 </file>
@@ -570,8 +586,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AFCA7E-B019-4751-9E70-78A52937EA85}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F887A687-8313-49C5-9098-E9EC8EB09C36}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -597,405 +656,521 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
         <v>29</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>31</v>
       </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" t="s">
-        <v>45</v>
-      </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="J12" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
         <v>29</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
         <v>27</v>
       </c>
-      <c r="H14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" t="s">
-        <v>53</v>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1004,42 +1179,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AFCA7E-B019-4751-9E70-78A52937EA85}">
-  <dimension ref="A1:A2"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8BB1619-25CA-4E08-A7C8-B671161E0367}">
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F887A687-8313-49C5-9098-E9EC8EB09C36}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2"/>
+      <c r="I2" s="4"/>
+      <c r="J2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0048829_VerifyStaffRoleChangesImplementedOnInternalTeamForCaptialSolution.xlsx
+++ b/TestData/LV_TMTT0048829_VerifyStaffRoleChangesImplementedOnInternalTeamForCaptialSolution.xlsx
@@ -8,27 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA25EFDB-50E1-4423-B13A-9E74A7C7F3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33685D64-0E05-4598-BBEC-7FCEC82D79F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppName" sheetId="3" r:id="rId1"/>
     <sheet name="ModuleName" sheetId="4" r:id="rId2"/>
-    <sheet name="UsersFinancial" sheetId="2" r:id="rId3"/>
-    <sheet name="UsersNonFinancial" sheetId="5" r:id="rId4"/>
+    <sheet name="UsersSet1" sheetId="2" r:id="rId3"/>
+    <sheet name="UsersSet2" sheetId="5" r:id="rId4"/>
+    <sheet name="UsersSet3" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="79">
   <si>
     <t>StdUser</t>
   </si>
@@ -243,7 +255,28 @@
     <t>TMTI0123353</t>
   </si>
   <si>
-    <t>TMTI0123299</t>
+    <t>Roxana Madrid</t>
+  </si>
+  <si>
+    <t>TMTI0123355</t>
+  </si>
+  <si>
+    <t>TMTI0123357</t>
+  </si>
+  <si>
+    <t>TMTI0123315</t>
+  </si>
+  <si>
+    <t>US Financial PFG</t>
+  </si>
+  <si>
+    <t>US Non-Financial PFG</t>
+  </si>
+  <si>
+    <t>OppRecordType</t>
+  </si>
+  <si>
+    <t>TMTI0123309</t>
   </si>
 </sst>
 </file>
@@ -1181,11 +1214,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8BB1619-25CA-4E08-A7C8-B671161E0367}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1215,7 +1254,7 @@
         <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>58</v>
@@ -1226,13 +1265,175 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F251A7-0E36-42D3-A443-4AAC6F49EAE5}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="2"/>
-      <c r="I2" s="4"/>
-      <c r="J2" t="s">
-        <v>71</v>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
